--- a/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -755,7 +755,7 @@
         <v>0.8446601941747572</v>
       </c>
       <c r="C14" t="n">
-        <v>0.865979381443299</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="D14" t="n">
         <v>0.8482142857142857</v>
@@ -764,7 +764,7 @@
         <v>0.8811881188118812</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8600104950360558</v>
+        <v>0.854855855860798</v>
       </c>
     </row>
     <row r="15">
@@ -777,16 +777,16 @@
         <v>0.4943181818181818</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="D15" t="n">
         <v>0.5945652173913043</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6441947565543071</v>
+        <v>0.6802434456928839</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5582695389409483</v>
+        <v>0.564305520749402</v>
       </c>
     </row>
     <row r="16">
@@ -799,16 +799,16 @@
         <v>0.4578947368421052</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4640883977900552</v>
+        <v>0.4581005586592179</v>
       </c>
       <c r="D16" t="n">
         <v>0.617286432160804</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6670329670329671</v>
+        <v>0.693939393939394</v>
       </c>
       <c r="F16" t="n">
-        <v>0.551575633456483</v>
+        <v>0.5568052804003802</v>
       </c>
     </row>
     <row r="17">
@@ -821,16 +821,16 @@
         <v>0.7824220746039856</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8037819673064874</v>
+        <v>0.7934112768530784</v>
       </c>
       <c r="D17" t="n">
         <v>0.8083991385498923</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8706125557610706</v>
+        <v>0.8764476447644765</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8163039340553589</v>
+        <v>0.8151700336928582</v>
       </c>
     </row>
     <row r="18">
@@ -843,16 +843,16 @@
         <v>0.7416666666666667</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6891025641025641</v>
+        <v>0.7188644688644688</v>
       </c>
       <c r="D18" t="n">
         <v>0.6505434782608696</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7757490636704121</v>
+        <v>0.7883895131086142</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7142654431751281</v>
+        <v>0.7248660317251548</v>
       </c>
     </row>
     <row r="19">
@@ -868,7 +868,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84, 0], [13, 0]]</t>
+          <t>[[82, 2], [13, 0]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[85, 4], [8, 4]]</t>
+          <t>[[84, 5], [7, 5]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[87, 2], [13, 2]]</t>
+          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8600104950360558</v>
+        <v>0.854855855860798</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01465351190524286</v>
+        <v>0.01526110791599093</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5582695389409483</v>
+        <v>0.564305520749402</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0636113876249941</v>
+        <v>0.0791572587858521</v>
       </c>
       <c r="J4" t="n">
-        <v>0.551575633456483</v>
+        <v>0.5568052804003802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09230172227263439</v>
+        <v>0.1024568842677156</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8163039340553589</v>
+        <v>0.8151700336928582</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03285076952941816</v>
+        <v>0.0365604395603386</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7142654431751281</v>
+        <v>0.7248660317251548</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0480227079978728</v>
+        <v>0.04969244090335814</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[87, 2], [13, 2]]</t>
+          <t>[[86, 2], [13, 2]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,16 +613,16 @@
         <v>0.8640776699029126</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8556701030927835</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8482142857142857</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8118811881188119</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8357891356110174</v>
+        <v>0.8475381312948274</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.7821969696969697</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7216117216117216</v>
+        <v>0.7275641025641025</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8521739130434782</v>
+        <v>0.8684782608695653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7794943820224719</v>
+        <v>0.7490636704119851</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7838692465936604</v>
+        <v>0.7818257508856556</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.7534199726402189</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7078313253012047</v>
+        <v>0.7203371035706365</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7899150391702526</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6758664955070603</v>
+        <v>0.6716852010265184</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7247556388383114</v>
+        <v>0.7338393291019065</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.870492608874663</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8599552850577566</v>
+        <v>0.8680599854129083</v>
       </c>
       <c r="D11" t="n">
-        <v>0.83843537414966</v>
+        <v>0.8610598824104285</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8300054652448556</v>
+        <v>0.8352471859675273</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8497221833317339</v>
+        <v>0.8587149156663818</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.8863636363636364</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8791208791208791</v>
+        <v>0.8891941391941391</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9081521739130435</v>
+        <v>0.9152173913043479</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8707865168539326</v>
+        <v>0.8548689138576779</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8861058015628729</v>
+        <v>0.8864110201799502</v>
       </c>
     </row>
     <row r="13">
@@ -726,22 +726,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[76, 8], [6, 7]]</t>
+          <t>[[77, 7], [6, 7]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[74, 18], [2, 18]]</t>
+          <t>[[77, 15], [2, 18]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[72, 17], [3, 9]]</t>
+          <t>[[74, 15], [4, 8]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[75, 13], [4, 11]]</t>
+          <t>[[77, 12], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8357891356110174</v>
+        <v>0.8475381312948274</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02522282748364869</v>
+        <v>0.02171123456797996</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7838692465936604</v>
+        <v>0.7818257508856556</v>
       </c>
       <c r="I3" t="n">
-        <v>0.046269490017</v>
+        <v>0.053680712750141</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7247556388383114</v>
+        <v>0.7338393291019065</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0349223499398285</v>
+        <v>0.04351244819632853</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8497221833317339</v>
+        <v>0.8587149156663818</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01621934016690776</v>
+        <v>0.01398461290244583</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8861058015628729</v>
+        <v>0.8864110201799502</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01387064019882546</v>
+        <v>0.02140361818288702</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[75, 13], [4, 11]]</t>
+          <t>[[77, 12], [4, 11]]</t>
         </is>
       </c>
     </row>
